--- a/SGC-CKN/Excel/39b0f70f-4add-40a2-abc8-c261e8ac1b9c_Hạng_mục_Lô_CT-02_P7-125_D800_28-01-2026.xlsx
+++ b/SGC-CKN/Excel/39b0f70f-4add-40a2-abc8-c261e8ac1b9c_Hạng_mục_Lô_CT-02_P7-125_D800_28-01-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="86">
   <si>
     <t>Dự án</t>
   </si>
@@ -53,13 +53,13 @@
     <t>Bắt đầu thi công</t>
   </si>
   <si>
-    <t>03:20 28/01/2026</t>
+    <t>03:20 28/03/2026</t>
   </si>
   <si>
     <t>Kết thúc thi công</t>
   </si>
   <si>
-    <t>18:05 28/01/2026</t>
+    <t>18:05 28/03/2026</t>
   </si>
   <si>
     <t>Địa chất TT</t>
@@ -95,15 +95,15 @@
     <t>1</t>
   </si>
   <si>
-    <t>Sét lẫn hữu cơ, xám nâu, xám đen TT dẻo chảy</t>
+    <t>Sét lẫn hữu cơ, xám nâu, xám đen, xám trắng, xám xanh TT dẻo chảy</t>
   </si>
   <si>
     <t xml:space="preserve">03:20
-28/01/2026</t>
+28/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">03:49
-28/01/2026</t>
+28/03/2026</t>
   </si>
   <si>
     <t>3h20 đến 3h49</t>
@@ -112,15 +112,15 @@
     <t>2</t>
   </si>
   <si>
-    <t>Cát pha xám ghi, xám nâu TT dẻo</t>
+    <t>Cát pha, xám ghi, xám nâu, xám vàng, TT dẻo</t>
   </si>
   <si>
     <t xml:space="preserve">03:50
-28/01/2026</t>
+28/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">03:56
-28/01/2026</t>
+28/03/2026</t>
   </si>
   <si>
     <t>3h50 đến 3h56</t>
@@ -133,11 +133,11 @@
   </si>
   <si>
     <t xml:space="preserve">03:57
-28/01/2026</t>
+28/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">04:40
-28/01/2026</t>
+28/03/2026</t>
   </si>
   <si>
     <t>3h57 đến 4h40</t>
@@ -146,15 +146,15 @@
     <t>4</t>
   </si>
   <si>
-    <t>Sét xám vàng, nâu vàng xám xanh TT nửa cứng</t>
+    <t>Sét xám vàng, nâu vàng, xám xanh, TT nửa cứng</t>
   </si>
   <si>
     <t xml:space="preserve">04:41
-28/01/2026</t>
+28/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">05:35
-28/01/2026</t>
+28/03/2026</t>
   </si>
   <si>
     <t>4h41 đến 5h35</t>
@@ -163,15 +163,15 @@
     <t>5</t>
   </si>
   <si>
-    <t>Cát thô vừa, xám vàng, xám xanh TT chặt lẫn sỏi sạn, có chỗ là cát hạt nhỏ, bụi</t>
+    <t>Cát thô vừa, xám vàng, xám xanh, TT chặt lẫn sỏi sạn, có chỗ là cát hạt nhỏ, bụi</t>
   </si>
   <si>
     <t xml:space="preserve">05:36
-28/01/2026</t>
+28/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">06:27
-28/01/2026</t>
+28/03/2026</t>
   </si>
   <si>
     <t>5h36 đến 6h27</t>
@@ -180,15 +180,15 @@
     <t>6</t>
   </si>
   <si>
-    <t>Cát thô, xám vàng, xám xanh, xám nâu KC chặt</t>
+    <t>Cát thô, xám vàng, xám xanh, xám nâu, KC chặt</t>
   </si>
   <si>
     <t xml:space="preserve">06:28
-28/01/2026</t>
+28/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">08:35
-28/01/2026</t>
+28/03/2026</t>
   </si>
   <si>
     <t>6h28 đến 8h35</t>
@@ -197,15 +197,15 @@
     <t>7</t>
   </si>
   <si>
-    <t>Sỏi xám vàng, xám xanh, TT rất chặt</t>
+    <t>Sỏi xám vàng, nâu vàng, xám xanh, TT rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">08:36
-28/01/2026</t>
+28/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">12:00
-28/01/2026</t>
+28/03/2026</t>
   </si>
   <si>
     <t>8h36 đến 12h00</t>
@@ -214,15 +214,15 @@
     <t>8</t>
   </si>
   <si>
-    <t>Cát xám, xám vàng, xám xanh, TT rất chặt</t>
+    <t>Cát xạm, xám vàng, xám xanh, TT rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">13:00
-28/01/2026</t>
+28/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">16:25
-28/01/2026</t>
+28/03/2026</t>
   </si>
   <si>
     <t>13h00 đến 16h25</t>
@@ -231,15 +231,12 @@
     <t>9</t>
   </si>
   <si>
-    <t>Sỏi xám vàng, xám xanh TT rất chặt</t>
-  </si>
-  <si>
     <t xml:space="preserve">16:26
-28/01/2026</t>
+28/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">17:30
-28/01/2026</t>
+28/03/2026</t>
   </si>
   <si>
     <t>16h26 đến 17h30</t>
@@ -248,15 +245,15 @@
     <t>10</t>
   </si>
   <si>
-    <t>Cuội đa màu sắc TT rất chặt</t>
+    <t>Cuội đa màu sắc, TT rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">17:31
-28/01/2026</t>
+28/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">18:05
-28/01/2026</t>
+28/03/2026</t>
   </si>
   <si>
     <t>17h31 đến 18h05</t>
@@ -1554,13 +1551,13 @@
         <v>11</v>
       </c>
       <c r="C19" s="33" t="s">
+        <v>57</v>
+      </c>
+      <c r="D19" s="34" t="s">
         <v>67</v>
       </c>
-      <c r="D19" s="34" t="s">
+      <c r="E19" s="34" t="s">
         <v>68</v>
-      </c>
-      <c r="E19" s="34" t="s">
-        <v>69</v>
       </c>
       <c r="F19" s="32">
         <v>-40</v>
@@ -1578,24 +1575,24 @@
         <v>3.54</v>
       </c>
       <c r="K19" s="33" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="20" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="35" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B20" s="35" t="s">
         <v>11</v>
       </c>
       <c r="C20" s="36" t="s">
+        <v>71</v>
+      </c>
+      <c r="D20" s="37" t="s">
         <v>72</v>
       </c>
-      <c r="D20" s="37" t="s">
+      <c r="E20" s="37" t="s">
         <v>73</v>
-      </c>
-      <c r="E20" s="37" t="s">
-        <v>74</v>
       </c>
       <c r="F20" s="35">
         <v>-43.78</v>
@@ -1613,12 +1610,12 @@
         <v>2.03</v>
       </c>
       <c r="K20" s="36" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="23" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="38" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B23" s="38"/>
       <c r="C23" s="38"/>
@@ -1724,31 +1721,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>83</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1991,7 +1988,7 @@
         <v>11</v>
       </c>
       <c r="C10" s="33" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="D10" s="32">
         <v>1</v>
@@ -2020,7 +2017,7 @@
         <v>11</v>
       </c>
       <c r="C11" s="36" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D11" s="35">
         <v>1</v>
@@ -2043,13 +2040,13 @@
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="39" t="s">
+        <v>84</v>
+      </c>
+      <c r="B12" s="40" t="s">
         <v>85</v>
       </c>
-      <c r="B12" s="40" t="s">
-        <v>86</v>
-      </c>
       <c r="C12" s="40" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D12" s="40">
         <v>10</v>

--- a/SGC-CKN/Excel/39b0f70f-4add-40a2-abc8-c261e8ac1b9c_Hạng_mục_Lô_CT-02_P7-125_D800_28-01-2026.xlsx
+++ b/SGC-CKN/Excel/39b0f70f-4add-40a2-abc8-c261e8ac1b9c_Hạng_mục_Lô_CT-02_P7-125_D800_28-01-2026.xlsx
@@ -1280,7 +1280,7 @@
         <v>29</v>
       </c>
       <c r="F11" s="5">
-        <v>-3.56</v>
+        <v>0</v>
       </c>
       <c r="G11" s="5">
         <v>-7.05</v>
@@ -1289,10 +1289,10 @@
         <v>0.48</v>
       </c>
       <c r="I11" s="5">
-        <v>3.49</v>
+        <v>7.05</v>
       </c>
       <c r="J11" s="8">
-        <v>7.22</v>
+        <v>14.59</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>30</v>
@@ -1762,7 +1762,7 @@
         <v>1</v>
       </c>
       <c r="E2" s="5">
-        <v>-3.56</v>
+        <v>0</v>
       </c>
       <c r="F2" s="5">
         <v>-7.05</v>
@@ -1771,10 +1771,10 @@
         <v>0.48</v>
       </c>
       <c r="H2" s="5">
-        <v>3.49</v>
+        <v>7.05</v>
       </c>
       <c r="I2" s="8">
-        <v>7.22</v>
+        <v>14.59</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2052,7 +2052,7 @@
         <v>10</v>
       </c>
       <c r="E12" s="40">
-        <v>-3.56</v>
+        <v>0</v>
       </c>
       <c r="F12" s="40">
         <v>-44.93</v>
@@ -2061,10 +2061,10 @@
         <v>13.62</v>
       </c>
       <c r="H12" s="40">
-        <v>41.37</v>
+        <v>44.93</v>
       </c>
       <c r="I12" s="40">
-        <v>3.04</v>
+        <v>3.3</v>
       </c>
     </row>
   </sheetData>
